--- a/ChartInformation.xlsx
+++ b/ChartInformation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCompany\8.SourceCode\3.Projects\20250601_AHD_QuanTrac\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3504ED47-1A2D-4C33-840D-96197637F012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C3156D-0C77-4B76-9EDD-27B6B1B5F4AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{F12BAEA0-A4E2-45FF-A2D3-E73D30EB81FF}"/>
   </bookViews>
@@ -31,7 +31,7 @@
     <author>ndcong</author>
   </authors>
   <commentList>
-    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{1954BE6A-340D-4E52-97C8-8164DD0F032D}">
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{1954BE6A-340D-4E52-97C8-8164DD0F032D}">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J5" authorId="0" shapeId="0" xr:uid="{1A4FD742-3E69-41EC-965B-5B1032A78728}">
+    <comment ref="M7" authorId="0" shapeId="0" xr:uid="{1A4FD742-3E69-41EC-965B-5B1032A78728}">
       <text>
         <r>
           <rPr>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t xml:space="preserve">Y - Mực nước (m): giá trị 17~28 </t>
   </si>
@@ -257,6 +257,27 @@
   </si>
   <si>
     <t>Q=2800</t>
+  </si>
+  <si>
+    <t>Line series</t>
+  </si>
+  <si>
+    <t>Line</t>
+  </si>
+  <si>
+    <t>area serires</t>
+  </si>
+  <si>
+    <t>Vùng_C: Cấp nước tăng cường = ĐPL</t>
+  </si>
+  <si>
+    <t>Vùng_B: Cấp nước bình thường = ĐPPH</t>
+  </si>
+  <si>
+    <t>Vùng_A: Vùng hạn chế cấp nước = HCCN</t>
+  </si>
+  <si>
+    <t>X -  (km):0~101</t>
   </si>
 </sst>
 </file>
@@ -323,7 +344,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -360,8 +381,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CEB99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6600"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -428,12 +467,58 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -450,7 +535,26 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -477,6 +581,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF6600"/>
+      <color rgb="FF00FFFF"/>
       <color rgb="FF0000FF"/>
       <color rgb="FF000000"/>
       <color rgb="FFFF33CC"/>
@@ -790,126 +896,110 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F46865B-9B69-40F5-9165-4F07FDCA0CD1}">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="87.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B5" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="16"/>
+      <c r="B6" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="K6" s="20"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="17"/>
+      <c r="B7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J7" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="M7" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>45839</v>
-      </c>
-      <c r="B6" s="5">
-        <v>28</v>
-      </c>
-      <c r="C6" s="5">
-        <v>26.92</v>
-      </c>
-      <c r="D6" s="5">
-        <v>25</v>
-      </c>
-      <c r="E6" s="5">
-        <v>24.4</v>
-      </c>
-      <c r="F6" s="5">
-        <v>20.3</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5">
-        <v>17</v>
-      </c>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>45854</v>
-      </c>
-      <c r="B7" s="5">
-        <v>28</v>
-      </c>
-      <c r="C7" s="5">
-        <v>26.92</v>
-      </c>
-      <c r="D7" s="5">
-        <v>25</v>
-      </c>
-      <c r="E7" s="5">
-        <v>24.4</v>
-      </c>
-      <c r="F7" s="5">
-        <v>21.2</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5">
-        <v>17</v>
-      </c>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>45869</v>
       </c>
       <c r="B8" s="5">
         <v>28</v>
@@ -924,18 +1014,21 @@
         <v>24.4</v>
       </c>
       <c r="F8" s="5">
-        <v>21.2</v>
+        <v>20.3</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
       <c r="I8" s="5">
         <v>17</v>
       </c>
-      <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="1"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>45884</v>
+        <v>45854</v>
       </c>
       <c r="B9" s="5">
         <v>28</v>
@@ -950,18 +1043,21 @@
         <v>24.4</v>
       </c>
       <c r="F9" s="5">
-        <v>22.7</v>
+        <v>21.2</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5">
         <v>17</v>
       </c>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="1"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>45899</v>
+        <v>45869</v>
       </c>
       <c r="B10" s="5">
         <v>28</v>
@@ -976,18 +1072,21 @@
         <v>24.4</v>
       </c>
       <c r="F10" s="5">
-        <v>22.7</v>
+        <v>21.2</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5">
         <v>17</v>
       </c>
-      <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="1"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>45914</v>
+        <v>45884</v>
       </c>
       <c r="B11" s="5">
         <v>28</v>
@@ -1002,18 +1101,21 @@
         <v>24.4</v>
       </c>
       <c r="F11" s="5">
-        <v>23.3</v>
+        <v>22.7</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5">
         <v>17</v>
       </c>
-      <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="1"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>45929</v>
+        <v>45899</v>
       </c>
       <c r="B12" s="5">
         <v>28</v>
@@ -1028,18 +1130,21 @@
         <v>24.4</v>
       </c>
       <c r="F12" s="5">
-        <v>23.65</v>
+        <v>22.7</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5">
         <v>17</v>
       </c>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="1"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>45944</v>
+        <v>45914</v>
       </c>
       <c r="B13" s="5">
         <v>28</v>
@@ -1054,18 +1159,21 @@
         <v>24.4</v>
       </c>
       <c r="F13" s="5">
-        <v>23.65</v>
+        <v>23.3</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5">
         <v>17</v>
       </c>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="1"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>45959</v>
+        <v>45929</v>
       </c>
       <c r="B14" s="5">
         <v>28</v>
@@ -1080,18 +1188,21 @@
         <v>24.4</v>
       </c>
       <c r="F14" s="5">
-        <v>24</v>
+        <v>23.65</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5">
         <v>17</v>
       </c>
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="1"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>45974</v>
+        <v>45944</v>
       </c>
       <c r="B15" s="5">
         <v>28</v>
@@ -1106,18 +1217,21 @@
         <v>24.4</v>
       </c>
       <c r="F15" s="5">
-        <v>24.3</v>
+        <v>23.65</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5">
         <v>17</v>
       </c>
-      <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="1"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>45989</v>
+        <v>45959</v>
       </c>
       <c r="B16" s="5">
         <v>28</v>
@@ -1132,18 +1246,21 @@
         <v>24.4</v>
       </c>
       <c r="F16" s="5">
-        <v>24.4</v>
+        <v>24</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5">
         <v>17</v>
       </c>
-      <c r="J16" s="1"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="1"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>46004</v>
+        <v>45974</v>
       </c>
       <c r="B17" s="5">
         <v>28</v>
@@ -1158,18 +1275,21 @@
         <v>24.4</v>
       </c>
       <c r="F17" s="5">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5">
         <v>17</v>
       </c>
-      <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="1"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>46019</v>
+        <v>45989</v>
       </c>
       <c r="B18" s="5">
         <v>28</v>
@@ -1183,17 +1303,22 @@
       <c r="E18" s="5">
         <v>24.4</v>
       </c>
-      <c r="F18" s="5"/>
+      <c r="F18" s="5">
+        <v>24.4</v>
+      </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5">
         <v>17</v>
       </c>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="1"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>46034</v>
+        <v>46004</v>
       </c>
       <c r="B19" s="5">
         <v>28</v>
@@ -1207,17 +1332,22 @@
       <c r="E19" s="5">
         <v>24.4</v>
       </c>
-      <c r="F19" s="5"/>
+      <c r="F19" s="5">
+        <v>24.4</v>
+      </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5">
         <v>17</v>
       </c>
-      <c r="J19" s="1"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="1"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>46049</v>
+        <v>46019</v>
       </c>
       <c r="B20" s="5">
         <v>28</v>
@@ -1237,11 +1367,14 @@
       <c r="I20" s="5">
         <v>17</v>
       </c>
-      <c r="J20" s="1"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="1"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>46064</v>
+        <v>46034</v>
       </c>
       <c r="B21" s="5">
         <v>28</v>
@@ -1261,11 +1394,14 @@
       <c r="I21" s="5">
         <v>17</v>
       </c>
-      <c r="J21" s="1"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="1"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>46079</v>
+        <v>46049</v>
       </c>
       <c r="B22" s="5">
         <v>28</v>
@@ -1285,11 +1421,14 @@
       <c r="I22" s="5">
         <v>17</v>
       </c>
-      <c r="J22" s="1"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="1"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>46094</v>
+        <v>46064</v>
       </c>
       <c r="B23" s="5">
         <v>28</v>
@@ -1309,11 +1448,14 @@
       <c r="I23" s="5">
         <v>17</v>
       </c>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="1"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>46109</v>
+        <v>46079</v>
       </c>
       <c r="B24" s="5">
         <v>28</v>
@@ -1333,11 +1475,14 @@
       <c r="I24" s="5">
         <v>17</v>
       </c>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="1"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>46124</v>
+        <v>46094</v>
       </c>
       <c r="B25" s="5">
         <v>28</v>
@@ -1357,11 +1502,14 @@
       <c r="I25" s="5">
         <v>17</v>
       </c>
-      <c r="J25" s="1"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="1"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>46139</v>
+        <v>46109</v>
       </c>
       <c r="B26" s="5">
         <v>28</v>
@@ -1381,11 +1529,14 @@
       <c r="I26" s="5">
         <v>17</v>
       </c>
-      <c r="J26" s="1"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="1"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>46154</v>
+        <v>46124</v>
       </c>
       <c r="B27" s="5">
         <v>28</v>
@@ -1405,11 +1556,14 @@
       <c r="I27" s="5">
         <v>17</v>
       </c>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="1"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>46169</v>
+        <v>46139</v>
       </c>
       <c r="B28" s="5">
         <v>28</v>
@@ -1429,11 +1583,14 @@
       <c r="I28" s="5">
         <v>17</v>
       </c>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="1"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>46184</v>
+        <v>46154</v>
       </c>
       <c r="B29" s="5">
         <v>28</v>
@@ -1453,11 +1610,14 @@
       <c r="I29" s="5">
         <v>17</v>
       </c>
-      <c r="J29" s="1"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="1"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>46199</v>
+        <v>46169</v>
       </c>
       <c r="B30" s="5">
         <v>28</v>
@@ -1477,12 +1637,71 @@
       <c r="I30" s="5">
         <v>17</v>
       </c>
-      <c r="J30" s="1"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="1"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B31" s="5">
+        <v>28</v>
+      </c>
+      <c r="C31" s="5">
+        <v>26.92</v>
+      </c>
+      <c r="D31" s="5">
+        <v>25</v>
+      </c>
+      <c r="E31" s="5">
+        <v>24.4</v>
+      </c>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5">
+        <v>17</v>
+      </c>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="1"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B32" s="5">
+        <v>28</v>
+      </c>
+      <c r="C32" s="5">
+        <v>26.92</v>
+      </c>
+      <c r="D32" s="5">
+        <v>25</v>
+      </c>
+      <c r="E32" s="5">
+        <v>24.4</v>
+      </c>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5">
+        <v>17</v>
+      </c>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:J4"/>
+  <mergeCells count="4">
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:M5"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="J6:L6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="256" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
@@ -1503,7 +1722,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1512,22 +1731,22 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="13" t="s">
+      <c r="B4" s="24"/>
+      <c r="C4" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
-      <c r="B5" s="17"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="26"/>
       <c r="C5" s="10" t="s">
         <v>51</v>
       </c>
